--- a/data/trans_camb/P16A_n_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 14,68</t>
+          <t>0,89; 14,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 8,76</t>
+          <t>-5,0; 7,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 16,45</t>
+          <t>3,25; 16,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 22,84</t>
+          <t>6,78; 23,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 12,05</t>
+          <t>-4,04; 11,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 17,0</t>
+          <t>3,76; 18,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 16,28</t>
+          <t>5,19; 16,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 8,25</t>
+          <t>-2,14; 7,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 15,21</t>
+          <t>4,31; 15,17</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 107,38</t>
+          <t>3,25; 100,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 60,73</t>
+          <t>-24,28; 57,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,4; 122,55</t>
+          <t>15,69; 116,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,43; 101,91</t>
+          <t>21,62; 104,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 52,16</t>
+          <t>-12,97; 48,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 77,39</t>
+          <t>12,27; 78,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,87; 84,02</t>
+          <t>20,34; 84,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 41,88</t>
+          <t>-8,95; 39,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,64; 80,24</t>
+          <t>15,66; 77,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 17,68</t>
+          <t>7,26; 17,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 14,02</t>
+          <t>4,28; 14,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 17,18</t>
+          <t>6,2; 17,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 16,75</t>
+          <t>4,68; 17,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 13,17</t>
+          <t>0,92; 12,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 13,14</t>
+          <t>2,1; 13,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 16,04</t>
+          <t>7,07; 15,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,11</t>
+          <t>3,76; 11,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 13,49</t>
+          <t>5,76; 13,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,27; 154,14</t>
+          <t>45,97; 163,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,71; 120,23</t>
+          <t>26,57; 123,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,62; 145,11</t>
+          <t>38,77; 144,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 60,87</t>
+          <t>14,05; 60,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 47,96</t>
+          <t>2,77; 45,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 46,75</t>
+          <t>6,8; 48,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,23; 80,99</t>
+          <t>28,2; 75,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 60,81</t>
+          <t>15,28; 58,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,88; 64,99</t>
+          <t>23,69; 68,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 20,33</t>
+          <t>6,78; 19,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 12,08</t>
+          <t>-0,28; 11,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,14; 25,5</t>
+          <t>12,5; 24,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,19; 24,21</t>
+          <t>9,73; 24,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 9,07</t>
+          <t>-3,97; 9,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 23,02</t>
+          <t>10,07; 23,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,66; 20,57</t>
+          <t>10,83; 20,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>-0,59; 8,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,19; 22,45</t>
+          <t>13,07; 22,22</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,57; 157,82</t>
+          <t>32,8; 147,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 91,97</t>
+          <t>-2,8; 87,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59,08; 203,6</t>
+          <t>65,01; 190,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,6; 102,63</t>
+          <t>31,59; 106,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 39,56</t>
+          <t>-13,89; 39,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,29; 98,05</t>
+          <t>32,61; 103,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,01; 107,05</t>
+          <t>45,9; 105,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 49,23</t>
+          <t>-2,45; 43,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54,83; 120,53</t>
+          <t>56,27; 116,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 12,74</t>
+          <t>0,22; 12,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 18,2</t>
+          <t>6,26; 19,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 24,07</t>
+          <t>9,58; 24,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 20,79</t>
+          <t>7,0; 21,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 19,15</t>
+          <t>4,97; 19,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 15,36</t>
+          <t>-10,28; 15,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 14,72</t>
+          <t>5,52; 14,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,88</t>
+          <t>7,27; 16,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 16,94</t>
+          <t>-0,2; 16,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 82,52</t>
+          <t>1,79; 83,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,36; 121,58</t>
+          <t>28,71; 126,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48,17; 158,46</t>
+          <t>45,34; 159,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,17; 73,47</t>
+          <t>19,87; 75,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,93; 67,99</t>
+          <t>14,14; 66,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 50,35</t>
+          <t>-30,8; 52,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,65; 64,99</t>
+          <t>20,82; 63,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,81; 74,03</t>
+          <t>27,99; 73,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 72,06</t>
+          <t>0,91; 71,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,48; 20,66</t>
+          <t>4,22; 20,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 11,84</t>
+          <t>-3,43; 11,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 21,46</t>
+          <t>6,48; 21,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,13; 27,83</t>
+          <t>8,43; 26,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 17,93</t>
+          <t>-0,48; 18,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 11,82</t>
+          <t>-18,15; 11,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,81; 21,48</t>
+          <t>8,28; 20,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 12,61</t>
+          <t>0,29; 12,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 14,51</t>
+          <t>-3,87; 14,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>23,13; 172,79</t>
+          <t>20,46; 169,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 99,24</t>
+          <t>-19,27; 88,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31,57; 179,38</t>
+          <t>33,36; 191,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,44; 89,56</t>
+          <t>20,68; 88,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 57,08</t>
+          <t>-1,53; 59,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,56; 35,87</t>
+          <t>-46,14; 35,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,38; 94,58</t>
+          <t>27,62; 90,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,18; 54,92</t>
+          <t>0,65; 54,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 61,86</t>
+          <t>-8,58; 65,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>7,68; 21,35</t>
+          <t>6,85; 21,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 8,95</t>
+          <t>-4,34; 9,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12,76; 26,43</t>
+          <t>12,84; 26,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,68; 22,75</t>
+          <t>6,18; 23,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 9,78</t>
+          <t>-5,8; 9,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,71; 22,5</t>
+          <t>7,24; 22,13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,65; 19,81</t>
+          <t>8,41; 19,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 7,12</t>
+          <t>-3,33; 7,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,86; 21,93</t>
+          <t>11,67; 21,9</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>35,45; 142,99</t>
+          <t>31,63; 145,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 57,51</t>
+          <t>-20,63; 64,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>59,35; 172,72</t>
+          <t>56,97; 182,89</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17,33; 90,26</t>
+          <t>18,25; 91,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 38,74</t>
+          <t>-17,86; 38,32</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,6; 90,64</t>
+          <t>21,52; 87,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,63; 91,37</t>
+          <t>30,9; 90,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 33,52</t>
+          <t>-13,14; 34,08</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>44,9; 103,4</t>
+          <t>42,14; 102,07</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,33</t>
+          <t>2,39; 11,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 8,06</t>
+          <t>-0,85; 8,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11,44; 22,74</t>
+          <t>12,36; 22,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,3; 14,93</t>
+          <t>4,64; 14,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 6,62</t>
+          <t>-3,43; 6,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,18; 50,96</t>
+          <t>14,28; 51,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,21; 11,8</t>
+          <t>4,77; 11,76</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 6,02</t>
+          <t>-0,46; 6,12</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,37; 45,45</t>
+          <t>15,45; 43,99</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,04; 72,97</t>
+          <t>12,81; 78,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 53,03</t>
+          <t>-4,3; 52,88</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>57,94; 147,19</t>
+          <t>61,71; 150,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,34; 58,67</t>
+          <t>14,57; 55,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 25,75</t>
+          <t>-11,43; 24,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>49,36; 203,74</t>
+          <t>47,85; 199,7</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,7; 54,21</t>
+          <t>19,75; 56,44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 27,86</t>
+          <t>-1,75; 28,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>63,64; 207,83</t>
+          <t>64,77; 203,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,32</t>
+          <t>-3,89; 4,74</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 8,61</t>
+          <t>-0,49; 8,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 4,03</t>
+          <t>-14,31; 3,85</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,54</t>
+          <t>-4,36; 5,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,17; 10,06</t>
+          <t>0,29; 9,85</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,81</t>
+          <t>0,94; 9,67</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,96</t>
+          <t>-2,61; 4,0</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,91</t>
+          <t>1,19; 7,65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 4,88</t>
+          <t>-11,56; 4,75</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 22,93</t>
+          <t>-16,96; 25,7</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 45,86</t>
+          <t>-2,17; 44,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 19,85</t>
+          <t>-63,49; 18,88</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 20,15</t>
+          <t>-12,97; 20,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,63; 36,37</t>
+          <t>0,72; 35,08</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,31; 35,35</t>
+          <t>2,3; 34,7</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 16,64</t>
+          <t>-9,47; 17,04</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>4,85; 33,38</t>
+          <t>4,42; 32,37</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 19,48</t>
+          <t>-40,01; 18,84</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,04</t>
+          <t>5,76; 9,61</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,53</t>
+          <t>3,58; 7,29</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4,69; 13,37</t>
+          <t>4,11; 13,19</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,57</t>
+          <t>7,8; 12,55</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,14</t>
+          <t>2,72; 7,37</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,81; 24,83</t>
+          <t>8,74; 23,49</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,69</t>
+          <t>7,51; 10,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,86</t>
+          <t>3,75; 6,74</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8,23; 17,89</t>
+          <t>8,36; 17,13</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>31,84; 60,41</t>
+          <t>31,36; 57,97</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>19,22; 45,27</t>
+          <t>19,65; 44,51</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>27,24; 79,39</t>
+          <t>23,44; 77,44</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>25,37; 43,76</t>
+          <t>25,13; 43,69</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,59; 24,98</t>
+          <t>8,55; 25,51</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>28,98; 81,85</t>
+          <t>28,86; 79,74</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>30,51; 46,76</t>
+          <t>30,29; 46,5</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15,0; 29,42</t>
+          <t>14,9; 29,39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>34,25; 76,79</t>
+          <t>34,48; 72,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,63</t>
+          <t>9,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,97</t>
+          <t>9,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 14,16</t>
+          <t>0,91; 15,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 7,93</t>
+          <t>-4,92; 7,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 16,72</t>
+          <t>2,71; 15,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 23,63</t>
+          <t>6,25; 22,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 11,44</t>
+          <t>-3,68; 12,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 18,03</t>
+          <t>1,71; 16,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 16,59</t>
+          <t>4,91; 16,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,77</t>
+          <t>-2,33; 8,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 15,17</t>
+          <t>4,79; 14,25</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 100,17</t>
+          <t>3,39; 109,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 57,46</t>
+          <t>-24,18; 52,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,69; 116,86</t>
+          <t>13,08; 112,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,62; 104,37</t>
+          <t>19,76; 95,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 48,48</t>
+          <t>-12,19; 55,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,27; 78,27</t>
+          <t>6,33; 73,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,34; 84,26</t>
+          <t>18,62; 86,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 39,47</t>
+          <t>-9,48; 43,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,66; 77,13</t>
+          <t>19,1; 73,99</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,52</t>
+          <t>11,67</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,63</t>
+          <t>9,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 17,83</t>
+          <t>7,08; 17,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,09</t>
+          <t>4,36; 14,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 17,2</t>
+          <t>6,41; 16,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 17,08</t>
+          <t>5,04; 17,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 12,64</t>
+          <t>1,04; 12,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 13,3</t>
+          <t>2,04; 12,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,46</t>
+          <t>7,35; 15,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,79</t>
+          <t>4,09; 12,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 13,74</t>
+          <t>5,6; 13,24</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,97; 163,43</t>
+          <t>43,21; 151,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,57; 123,79</t>
+          <t>27,56; 121,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,77; 144,06</t>
+          <t>39,2; 137,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 60,61</t>
+          <t>14,77; 62,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 45,73</t>
+          <t>3,11; 47,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 48,38</t>
+          <t>5,49; 45,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,2; 75,47</t>
+          <t>30,96; 77,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,28; 58,31</t>
+          <t>16,46; 61,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 68,16</t>
+          <t>23,21; 63,45</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,72</t>
+          <t>19,57</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,88</t>
+          <t>17,16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,89</t>
+          <t>18,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 19,85</t>
+          <t>6,97; 20,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 11,41</t>
+          <t>0,23; 12,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,5; 24,66</t>
+          <t>13,08; 26,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 24,42</t>
+          <t>9,49; 24,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 9,26</t>
+          <t>-4,65; 9,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,07; 23,1</t>
+          <t>10,57; 23,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 20,43</t>
+          <t>10,6; 20,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,41</t>
+          <t>-0,51; 9,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 22,22</t>
+          <t>13,69; 22,9</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117,4%</t>
+          <t>122,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,8; 147,61</t>
+          <t>38,62; 157,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 87,5</t>
+          <t>0,43; 99,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65,01; 190,3</t>
+          <t>66,25; 203,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,59; 106,79</t>
+          <t>31,09; 103,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 39,5</t>
+          <t>-15,1; 40,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,61; 103,9</t>
+          <t>35,93; 106,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,9; 105,94</t>
+          <t>44,63; 109,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 43,33</t>
+          <t>-1,71; 48,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56,27; 116,87</t>
+          <t>57,44; 120,87</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,41</t>
+          <t>14,65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>13,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,63</t>
+          <t>14,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 12,35</t>
+          <t>0,15; 12,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 19,02</t>
+          <t>5,67; 18,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,58; 24,5</t>
+          <t>7,46; 21,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 21,1</t>
+          <t>6,87; 20,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 19,18</t>
+          <t>4,98; 19,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 15,57</t>
+          <t>6,49; 20,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 14,55</t>
+          <t>5,3; 14,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,69</t>
+          <t>7,22; 17,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 16,84</t>
+          <t>9,45; 19,05</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 83,97</t>
+          <t>0,54; 84,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,71; 126,93</t>
+          <t>25,26; 123,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,34; 159,98</t>
+          <t>37,09; 142,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,87; 75,78</t>
+          <t>19,99; 69,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,14; 66,79</t>
+          <t>13,95; 65,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 52,11</t>
+          <t>18,29; 71,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,82; 63,29</t>
+          <t>18,32; 64,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,99; 73,47</t>
+          <t>25,97; 74,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 71,38</t>
+          <t>34,78; 84,2</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>12,2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>9,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,22; 20,07</t>
+          <t>3,74; 20,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 11,09</t>
+          <t>-3,72; 11,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 21,23</t>
+          <t>4,79; 19,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,43; 26,67</t>
+          <t>8,28; 26,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 18,69</t>
+          <t>-0,69; 17,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 11,69</t>
+          <t>-2,13; 15,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,28; 20,92</t>
+          <t>8,52; 21,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 12,33</t>
+          <t>0,26; 12,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 14,95</t>
+          <t>4,43; 15,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>20,46; 169,16</t>
+          <t>18,55; 164,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 88,98</t>
+          <t>-19,65; 92,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33,36; 191,37</t>
+          <t>25,47; 163,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,68; 88,63</t>
+          <t>19,96; 87,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 59,75</t>
+          <t>-2,71; 55,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 35,3</t>
+          <t>-4,79; 51,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,62; 90,94</t>
+          <t>28,99; 95,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,65; 54,31</t>
+          <t>0,9; 57,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 65,41</t>
+          <t>15,68; 68,09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19,45</t>
+          <t>18,59</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,93</t>
+          <t>15,06</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17,03</t>
+          <t>16,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6,85; 21,43</t>
+          <t>6,82; 21,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 9,52</t>
+          <t>-3,92; 9,4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12,84; 26,64</t>
+          <t>11,17; 25,19</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,18; 23,03</t>
+          <t>6,18; 21,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 9,56</t>
+          <t>-6,68; 9,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,24; 22,13</t>
+          <t>7,83; 21,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,41; 19,43</t>
+          <t>8,99; 20,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 7,09</t>
+          <t>-2,63; 7,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,67; 21,9</t>
+          <t>11,76; 21,68</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>107,46%</t>
+          <t>102,74%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>70,16%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31,63; 145,65</t>
+          <t>33,43; 153,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 64,79</t>
+          <t>-19,17; 65,1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>56,97; 182,89</t>
+          <t>48,65; 169,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18,25; 91,17</t>
+          <t>18,84; 87,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 38,32</t>
+          <t>-21,37; 35,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,52; 87,18</t>
+          <t>23,86; 86,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,9; 90,8</t>
+          <t>34,58; 94,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 34,08</t>
+          <t>-10,16; 37,99</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42,14; 102,07</t>
+          <t>44,17; 107,16</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>18,42</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,43</t>
+          <t>15,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>25,02</t>
+          <t>17,23</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,39; 11,8</t>
+          <t>2,24; 11,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 8,1</t>
+          <t>-0,52; 8,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12,36; 22,89</t>
+          <t>13,3; 23,36</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,49</t>
+          <t>4,03; 14,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 6,35</t>
+          <t>-3,41; 6,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,28; 51,65</t>
+          <t>10,98; 20,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,76</t>
+          <t>4,8; 11,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,12</t>
+          <t>-0,71; 6,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,45; 43,99</t>
+          <t>13,68; 21,21</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>105,6%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>103,68%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>108,73%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,81; 78,12</t>
+          <t>10,68; 75,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 52,88</t>
+          <t>-2,75; 55,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>61,71; 150,66</t>
+          <t>66,49; 151,16</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,57; 55,57</t>
+          <t>13,23; 57,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 24,95</t>
+          <t>-11,23; 25,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,85; 199,7</t>
+          <t>35,4; 82,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,75; 56,44</t>
+          <t>18,55; 54,46</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 28,96</t>
+          <t>-2,87; 29,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>64,77; 203,1</t>
+          <t>56,24; 100,08</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>2,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 4,74</t>
+          <t>-4,37; 4,48</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,17</t>
+          <t>-0,33; 8,6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 3,85</t>
+          <t>-2,24; 6,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 5,74</t>
+          <t>-3,73; 5,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,85</t>
+          <t>0,64; 10,71</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,67</t>
+          <t>-0,53; 8,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,0</t>
+          <t>-2,28; 3,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,65</t>
+          <t>1,44; 7,85</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 4,75</t>
+          <t>-0,16; 6,23</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-17,39%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-1,92%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 25,7</t>
+          <t>-18,72; 24,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 44,46</t>
+          <t>-1,62; 47,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-63,49; 18,88</t>
+          <t>-9,98; 34,3</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 20,64</t>
+          <t>-11,43; 21,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,72; 35,08</t>
+          <t>1,72; 38,22</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,3; 34,7</t>
+          <t>-1,83; 29,85</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 17,04</t>
+          <t>-8,38; 16,12</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>4,42; 32,37</t>
+          <t>5,39; 33,62</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 18,84</t>
+          <t>-0,39; 26,51</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>12,16</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11,81</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,61</t>
+          <t>5,84; 9,78</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,29</t>
+          <t>3,64; 7,42</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,19</t>
+          <t>10,15; 14,48</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,55</t>
+          <t>7,98; 12,48</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,37</t>
+          <t>2,72; 7,32</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,74; 23,49</t>
+          <t>8,79; 12,82</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,68</t>
+          <t>7,51; 10,55</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,74</t>
+          <t>3,81; 6,82</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,13</t>
+          <t>9,7; 12,93</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>31,36; 57,97</t>
+          <t>31,42; 59,59</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>19,65; 44,51</t>
+          <t>20,11; 45,27</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>23,44; 77,44</t>
+          <t>54,61; 86,75</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>25,13; 43,69</t>
+          <t>25,46; 43,08</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,55; 25,51</t>
+          <t>8,66; 25,58</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>28,86; 79,74</t>
+          <t>28,39; 44,74</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>30,29; 46,5</t>
+          <t>31,01; 46,19</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14,9; 29,39</t>
+          <t>15,58; 29,81</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>34,48; 72,37</t>
+          <t>39,77; 56,61</t>
         </is>
       </c>
     </row>
